--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>264</v>
+        <v>411</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
